--- a/XB6A/5. KL đắp lề - XB6A.xlsx
+++ b/XB6A/5. KL đắp lề - XB6A.xlsx
@@ -131,7 +131,7 @@
     <t xml:space="preserve">PHỤ LỤC KIỂM TRA CAO ĐỘ, KÍCH THƯỚC HÌNH HỌC</t>
   </si>
   <si>
-    <t xml:space="preserve">Kèm theo BBNT số: 18.NĐXB6A/CVXD ngày 03 tháng 09 năm 2026</t>
+    <t xml:space="preserve">Kèm theo BBNT số: 18.NĐXB6A/CVXD ngày 06 tháng 09 năm 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Dự án: Xây dựng HTKT Khu tái định cư phục vụ di dân xã Hải Hà, thị xã Nghi Sơn, tỉnh Thanh Hóa.</t>
@@ -218,19 +218,19 @@
     <t xml:space="preserve">                 </t>
   </si>
   <si>
-    <t xml:space="preserve">Kèm theo BBNT số: 20.NĐXB6A/CVXD ngày 04 tháng 09 năm 2026</t>
+    <t xml:space="preserve">Kèm theo BBNT số: 20.NĐXB6A/CVXD ngày 07 tháng 09 năm 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Đắp đất lề đường lớp 2, độ chặt K&gt;=0,95 đoạn từ Km0+000,00 - Km0+126,46</t>
   </si>
   <si>
-    <t xml:space="preserve">Kèm theo BBNT số: 22.NĐXB6A/CVXD ngày 05 tháng 09 năm 2026</t>
+    <t xml:space="preserve">Kèm theo BBNT số: 22.NĐXB6A/CVXD ngày 08 tháng 09 năm 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Đắp đất lề đường lớp 3, độ chặt K&gt;=0,95 đoạn từ Km0+000,00 - Km0+126,46</t>
   </si>
   <si>
-    <t xml:space="preserve">Kèm theo BBNT số: 23.NĐXB6A/CVXD ngày 06 tháng 09 năm 2026</t>
+    <t xml:space="preserve">Kèm theo BBNT số: 23.NĐXB6A/CVXD ngày 09 tháng 09 năm 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Đắp đất lề đường lớp 4, độ chặt K&gt;=0,95 đoạn từ Km0+000,00 - Km0+126,46</t>
@@ -1077,7 +1077,7 @@
             <v xml:space="preserve">Kiểm tra cao độ đường đen đoạn từ Km0+000,00 -:- Km0+126,46</v>
           </cell>
           <cell r="D3" t="str">
-            <v xml:space="preserve">ngày 14 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 20 tháng 08 năm 2026</v>
           </cell>
           <cell r="G3" t="str">
             <v xml:space="preserve">01.NĐXB6A/CVXD </v>
@@ -1091,7 +1091,7 @@
             <v xml:space="preserve">Đào đất xử lý nền đường đoạn từ Km0+000,00 - Km0+126,46</v>
           </cell>
           <cell r="D4" t="str">
-            <v xml:space="preserve">ngày 15 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 24 tháng 08 năm 2026</v>
           </cell>
           <cell r="G4" t="str">
             <v xml:space="preserve">02.NĐXB6A/CVXD </v>
@@ -1105,7 +1105,7 @@
             <v xml:space="preserve">Rải vải địa kỹ thuật đoạn từ Km0+000,00 - Km0+126,46</v>
           </cell>
           <cell r="D5" t="str">
-            <v xml:space="preserve">ngày 15 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 24 tháng 08 năm 2026</v>
           </cell>
           <cell r="G5" t="str">
             <v xml:space="preserve">03.NĐXB6A/CVXD </v>
@@ -1119,7 +1119,7 @@
             <v xml:space="preserve">Đắp cát nền đường lớp 1 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D6" t="str">
-            <v xml:space="preserve">ngày 16 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 25 tháng 08 năm 2026</v>
           </cell>
           <cell r="G6" t="str">
             <v xml:space="preserve">04.NĐXB6A/CVXD </v>
@@ -1133,7 +1133,7 @@
             <v xml:space="preserve">Đắp cát nền đường lớp 2 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D7" t="str">
-            <v xml:space="preserve">ngày 17 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 26 tháng 08 năm 2026</v>
           </cell>
           <cell r="G7" t="str">
             <v xml:space="preserve">05.NĐXB6A/CVXD </v>
@@ -1147,7 +1147,7 @@
             <v xml:space="preserve">Đắp cát nền đường lớp 3 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D8" t="str">
-            <v xml:space="preserve">ngày 24 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 27 tháng 08 năm 2026</v>
           </cell>
           <cell r="G8" t="str">
             <v xml:space="preserve">06.NĐXB6A/CVXD </v>
@@ -1161,7 +1161,7 @@
             <v xml:space="preserve">Đắp cát nền đường lớp 4 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D9" t="str">
-            <v xml:space="preserve">ngày 25 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 28 tháng 08 năm 2026</v>
           </cell>
           <cell r="G9" t="str">
             <v xml:space="preserve">07.NĐXB6A/CVXD </v>
@@ -1175,7 +1175,7 @@
             <v xml:space="preserve">Đắp đất nền đường lớp 1 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D10" t="str">
-            <v xml:space="preserve">ngày 26 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 29 tháng 08 năm 2026</v>
           </cell>
           <cell r="G10" t="str">
             <v xml:space="preserve">08.NĐXB6A/CVXD </v>
@@ -1189,7 +1189,7 @@
             <v xml:space="preserve">Đắp đất nền đường lớp 2 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D11" t="str">
-            <v xml:space="preserve">ngày 26 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 29 tháng 08 năm 2026</v>
           </cell>
           <cell r="G11" t="str">
             <v xml:space="preserve">09.NĐXB6A/CVXD </v>
@@ -1203,7 +1203,7 @@
             <v xml:space="preserve">Đắp đất nền đường lớp 3 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D12" t="str">
-            <v xml:space="preserve">ngày 27 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 30 tháng 08 năm 2026</v>
           </cell>
           <cell r="G12" t="str">
             <v xml:space="preserve">10.NĐXB6A/CVXD </v>
@@ -1217,7 +1217,7 @@
             <v xml:space="preserve">Đắp đất nền đường lớp 4 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D13" t="str">
-            <v xml:space="preserve">ngày 27 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 30 tháng 08 năm 2026</v>
           </cell>
           <cell r="G13" t="str">
             <v xml:space="preserve">11.NĐXB6A/CVXD </v>
@@ -1231,7 +1231,7 @@
             <v xml:space="preserve">Đắp đất nền đường lớp 5 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D14" t="str">
-            <v xml:space="preserve">ngày 28 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 03 tháng 09 năm 2026</v>
           </cell>
           <cell r="G14" t="str">
             <v xml:space="preserve">12.NĐXB6A/CVXD </v>
@@ -1245,7 +1245,7 @@
             <v xml:space="preserve">Đắp đất nền đường lớp 6 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D15" t="str">
-            <v xml:space="preserve">ngày 28 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 03 tháng 09 năm 2026</v>
           </cell>
           <cell r="G15" t="str">
             <v xml:space="preserve">13.NĐXB6A/CVXD </v>
@@ -1259,7 +1259,7 @@
             <v xml:space="preserve">Đắp đất nền đường lớp 7 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D16" t="str">
-            <v xml:space="preserve">ngày 29 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 04 tháng 09 năm 2026</v>
           </cell>
           <cell r="G16" t="str">
             <v xml:space="preserve">14.NĐXB6A/CVXD </v>
@@ -1273,7 +1273,7 @@
             <v xml:space="preserve">Đắp đất nền đường lớp 8 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D17" t="str">
-            <v xml:space="preserve">ngày 29 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 04 tháng 09 năm 2026</v>
           </cell>
           <cell r="G17" t="str">
             <v xml:space="preserve">15.NĐXB6A/CVXD </v>
@@ -1287,7 +1287,7 @@
             <v xml:space="preserve">Đắp đất nền đường lớp 9 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D18" t="str">
-            <v xml:space="preserve">ngày 30 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 05 tháng 09 năm 2026</v>
           </cell>
           <cell r="G18" t="str">
             <v xml:space="preserve">16.NĐXB6A/CVXD </v>
@@ -1301,7 +1301,7 @@
             <v xml:space="preserve">Đắp đất nền đường lớp 1, độ chặt K&gt;=0,98 đoạn từ Km0+000,00 - Km0+126,46</v>
           </cell>
           <cell r="D19" t="str">
-            <v xml:space="preserve">ngày 03 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 06 tháng 09 năm 2026</v>
           </cell>
           <cell r="G19" t="str">
             <v xml:space="preserve">17.NĐXB6A/CVXD </v>
@@ -1315,7 +1315,7 @@
             <v xml:space="preserve">Đắp đất lề đường lớp 1, độ chặt K&gt;=0,95 đoạn từ Km0+000,00 - Km0+126,46</v>
           </cell>
           <cell r="D20" t="str">
-            <v xml:space="preserve">ngày 03 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 06 tháng 09 năm 2026</v>
           </cell>
           <cell r="G20" t="str">
             <v xml:space="preserve">18.NĐXB6A/CVXD </v>
@@ -1329,7 +1329,7 @@
             <v xml:space="preserve">Đắp đất nền đường lớp 2, độ chặt K&gt;=0,98 đoạn từ Km0+000,00 - Km0+126,46</v>
           </cell>
           <cell r="D21" t="str">
-            <v xml:space="preserve">ngày 04 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 07 tháng 09 năm 2026</v>
           </cell>
           <cell r="G21" t="str">
             <v xml:space="preserve">19.NĐXB6A/CVXD </v>
@@ -1343,7 +1343,7 @@
             <v xml:space="preserve">Đắp đất lề đường lớp 2, độ chặt K&gt;=0,95 đoạn từ Km0+000,00 - Km0+126,46</v>
           </cell>
           <cell r="D22" t="str">
-            <v xml:space="preserve">ngày 04 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 07 tháng 09 năm 2026</v>
           </cell>
           <cell r="G22" t="str">
             <v xml:space="preserve">20.NĐXB6A/CVXD </v>
@@ -1357,7 +1357,7 @@
             <v xml:space="preserve">Đắp cấp phối đá dăm loại 2 đoạn từ Km0+000,00 - Km0+126,46</v>
           </cell>
           <cell r="D23" t="str">
-            <v xml:space="preserve">ngày 05 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 08 tháng 09 năm 2026</v>
           </cell>
           <cell r="G23" t="str">
             <v xml:space="preserve">21.NĐXB6A/CVXD </v>
@@ -1371,7 +1371,7 @@
             <v xml:space="preserve">Đắp đất lề đường lớp 3, độ chặt K&gt;=0,95 đoạn từ Km0+000,00 - Km0+126,46</v>
           </cell>
           <cell r="D24" t="str">
-            <v xml:space="preserve">ngày 05 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 08 tháng 09 năm 2026</v>
           </cell>
           <cell r="G24" t="str">
             <v xml:space="preserve">22.NĐXB6A/CVXD </v>
@@ -1385,7 +1385,7 @@
             <v xml:space="preserve">Đắp đất lề đường lớp 4, độ chặt K&gt;=0,95 đoạn từ Km0+000,00 - Km0+126,46</v>
           </cell>
           <cell r="D25" t="str">
-            <v xml:space="preserve">ngày 06 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 09 tháng 09 năm 2026</v>
           </cell>
           <cell r="G25" t="str">
             <v xml:space="preserve">23.NĐXB6A/CVXD </v>
@@ -1399,7 +1399,7 @@
             <v xml:space="preserve">Đắp cấp phối đá dăm loại 1 đoạn từ Km0+000,00 - Km0+126,46</v>
           </cell>
           <cell r="D26" t="str">
-            <v xml:space="preserve">ngày 06 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 09 tháng 09 năm 2026</v>
           </cell>
           <cell r="G26" t="str">
             <v xml:space="preserve">24.NĐXB6A/CVXD </v>
@@ -1413,7 +1413,7 @@
             <v xml:space="preserve">Vệ sinh, thổi bụi mặt đường </v>
           </cell>
           <cell r="D27" t="str">
-            <v xml:space="preserve">ngày 08 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 11 tháng 09 năm 2026</v>
           </cell>
           <cell r="G27" t="str">
             <v xml:space="preserve">25.NĐXB6A/CVXD </v>
@@ -1427,7 +1427,7 @@
             <v xml:space="preserve">Tưới lớp thấm bám mặt đường, nhựa MC70, lượng nhựa 1kg/m2</v>
           </cell>
           <cell r="D28" t="str">
-            <v xml:space="preserve">ngày 10 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 13 tháng 09 năm 2026</v>
           </cell>
           <cell r="G28" t="str">
             <v xml:space="preserve">26.NĐXB6A/CVXD </v>
@@ -1441,7 +1441,7 @@
             <v xml:space="preserve">Rải thảm mặt đường bê tông nhựa C16 - Chiều dày mặt đường đã lèn ép 6cm</v>
           </cell>
           <cell r="D29" t="str">
-            <v xml:space="preserve">ngày 12 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 19 tháng 09 năm 2026</v>
           </cell>
           <cell r="G29" t="str">
             <v xml:space="preserve">27.NĐXB6A/CVXD </v>
@@ -1455,7 +1455,7 @@
             <v xml:space="preserve">Bê tông nhựa C16 - Chiều dày mặt đường đã lèn ép 6cm</v>
           </cell>
           <cell r="D30" t="str">
-            <v xml:space="preserve">ngày 19 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 21 tháng 09 năm 2026</v>
           </cell>
           <cell r="G30" t="str">
             <v xml:space="preserve">28.NĐXB6A/CVXD </v>
@@ -4778,7 +4778,7 @@
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="str">
         <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,4,0)</f>
-        <v xml:space="preserve">Kèm theo BBNT số: 18.NĐXB6A/CVXD ngày 03 tháng 09 năm 2026</v>
+        <v xml:space="preserve">Kèm theo BBNT số: 18.NĐXB6A/CVXD ngày 06 tháng 09 năm 2026</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -5022,11 +5022,11 @@
       </c>
       <c r="E21" s="16" t="n">
         <f aca="false">D21+F21</f>
-        <v>2.157</v>
+        <v>2.065</v>
       </c>
       <c r="F21" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.067</v>
+        <v>-0.025</v>
       </c>
       <c r="G21" s="16" t="n">
         <f aca="false">Chạy!I5</f>
@@ -5034,11 +5034,11 @@
       </c>
       <c r="H21" s="16" t="n">
         <f aca="false">G21+I21</f>
-        <v>2.105</v>
+        <v>2.174</v>
       </c>
       <c r="I21" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.015</v>
+        <v>0.084</v>
       </c>
       <c r="J21" s="16" t="n">
         <f aca="false">Chạy!M9</f>
@@ -5046,11 +5046,11 @@
       </c>
       <c r="K21" s="16" t="n">
         <f aca="false">J21+L21</f>
-        <v>2.138</v>
+        <v>2.19</v>
       </c>
       <c r="L21" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.048</v>
+        <v>0.1</v>
       </c>
       <c r="M21" s="16" t="n">
         <f aca="false">Chạy!O9</f>
@@ -5058,11 +5058,11 @@
       </c>
       <c r="N21" s="16" t="n">
         <f aca="false">M21+O21</f>
-        <v>2.153</v>
+        <v>2.072</v>
       </c>
       <c r="O21" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.063</v>
+        <v>-0.018</v>
       </c>
       <c r="P21" s="17"/>
       <c r="Q21" s="18" t="n">
@@ -5086,11 +5086,11 @@
       </c>
       <c r="E22" s="16" t="n">
         <f aca="false">D22+F22</f>
-        <v>2.098</v>
+        <v>2.161</v>
       </c>
       <c r="F22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.008</v>
+        <v>0.071</v>
       </c>
       <c r="G22" s="16" t="n">
         <f aca="false">Chạy!I13</f>
@@ -5098,11 +5098,11 @@
       </c>
       <c r="H22" s="16" t="n">
         <f aca="false">G22+I22</f>
-        <v>2.169</v>
+        <v>2.131</v>
       </c>
       <c r="I22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.079</v>
+        <v>0.041</v>
       </c>
       <c r="J22" s="16" t="n">
         <f aca="false">Chạy!M17</f>
@@ -5110,11 +5110,11 @@
       </c>
       <c r="K22" s="16" t="n">
         <f aca="false">J22+L22</f>
-        <v>2.17</v>
+        <v>2.186</v>
       </c>
       <c r="L22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.08</v>
+        <v>0.096</v>
       </c>
       <c r="M22" s="16" t="n">
         <f aca="false">Chạy!O17</f>
@@ -5122,11 +5122,11 @@
       </c>
       <c r="N22" s="16" t="n">
         <f aca="false">M22+O22</f>
-        <v>2.1</v>
+        <v>2.187</v>
       </c>
       <c r="O22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.01</v>
+        <v>0.097</v>
       </c>
       <c r="P22" s="17"/>
       <c r="Q22" s="18" t="n">
@@ -5150,11 +5150,11 @@
       </c>
       <c r="E23" s="16" t="n">
         <f aca="false">D23+F23</f>
-        <v>2.102</v>
+        <v>2.08</v>
       </c>
       <c r="F23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.002</v>
+        <v>-0.02</v>
       </c>
       <c r="G23" s="16" t="n">
         <f aca="false">Chạy!I21</f>
@@ -5162,11 +5162,11 @@
       </c>
       <c r="H23" s="16" t="n">
         <f aca="false">G23+I23</f>
-        <v>2.077</v>
+        <v>2.13</v>
       </c>
       <c r="I23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>-0.023</v>
+        <v>0.03</v>
       </c>
       <c r="J23" s="16" t="n">
         <f aca="false">Chạy!M25</f>
@@ -5174,11 +5174,11 @@
       </c>
       <c r="K23" s="16" t="n">
         <f aca="false">J23+L23</f>
-        <v>2.13</v>
+        <v>2.197</v>
       </c>
       <c r="L23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.03</v>
+        <v>0.097</v>
       </c>
       <c r="M23" s="16" t="n">
         <f aca="false">Chạy!O25</f>
@@ -5186,11 +5186,11 @@
       </c>
       <c r="N23" s="16" t="n">
         <f aca="false">M23+O23</f>
-        <v>2.151</v>
+        <v>2.128</v>
       </c>
       <c r="O23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.051</v>
+        <v>0.028</v>
       </c>
       <c r="P23" s="17"/>
       <c r="Q23" s="18" t="n">
@@ -5226,11 +5226,11 @@
       </c>
       <c r="H24" s="16" t="n">
         <f aca="false">G24+I24</f>
-        <v>2.163</v>
+        <v>2.106</v>
       </c>
       <c r="I24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.053</v>
+        <v>-0.004</v>
       </c>
       <c r="J24" s="16" t="n">
         <f aca="false">Chạy!M33</f>
@@ -5238,11 +5238,11 @@
       </c>
       <c r="K24" s="16" t="n">
         <f aca="false">J24+L24</f>
-        <v>2.206</v>
+        <v>2.21</v>
       </c>
       <c r="L24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.096</v>
+        <v>0.1</v>
       </c>
       <c r="M24" s="16" t="n">
         <f aca="false">Chạy!O33</f>
@@ -5250,11 +5250,11 @@
       </c>
       <c r="N24" s="16" t="n">
         <f aca="false">M24+O24</f>
-        <v>2.153</v>
+        <v>2.116</v>
       </c>
       <c r="O24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.043</v>
+        <v>0.006</v>
       </c>
       <c r="P24" s="17"/>
       <c r="Q24" s="18" t="n">
@@ -5278,11 +5278,11 @@
       </c>
       <c r="E25" s="16" t="n">
         <f aca="false">D25+F25</f>
-        <v>2.187</v>
+        <v>2.206</v>
       </c>
       <c r="F25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.077</v>
+        <v>0.096</v>
       </c>
       <c r="G25" s="16" t="n">
         <f aca="false">Chạy!I37</f>
@@ -5290,11 +5290,11 @@
       </c>
       <c r="H25" s="16" t="n">
         <f aca="false">G25+I25</f>
-        <v>2.164</v>
+        <v>2.162</v>
       </c>
       <c r="I25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.054</v>
+        <v>0.052</v>
       </c>
       <c r="J25" s="16" t="n">
         <f aca="false">Chạy!M41</f>
@@ -5302,11 +5302,11 @@
       </c>
       <c r="K25" s="16" t="n">
         <f aca="false">J25+L25</f>
-        <v>2.162</v>
+        <v>2.135</v>
       </c>
       <c r="L25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.052</v>
+        <v>0.025</v>
       </c>
       <c r="M25" s="16" t="n">
         <f aca="false">Chạy!O41</f>
@@ -5314,11 +5314,11 @@
       </c>
       <c r="N25" s="16" t="n">
         <f aca="false">M25+O25</f>
-        <v>2.199</v>
+        <v>2.19</v>
       </c>
       <c r="O25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.089</v>
+        <v>0.08</v>
       </c>
       <c r="P25" s="17"/>
       <c r="Q25" s="18" t="n">
@@ -5342,11 +5342,11 @@
       </c>
       <c r="E26" s="16" t="n">
         <f aca="false">D26+F26</f>
-        <v>2.135</v>
+        <v>2.188</v>
       </c>
       <c r="F26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.015</v>
+        <v>0.068</v>
       </c>
       <c r="G26" s="16" t="n">
         <f aca="false">Chạy!I45</f>
@@ -5354,11 +5354,11 @@
       </c>
       <c r="H26" s="16" t="n">
         <f aca="false">G26+I26</f>
-        <v>2.166</v>
+        <v>2.168</v>
       </c>
       <c r="I26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.046</v>
+        <v>0.048</v>
       </c>
       <c r="J26" s="16" t="n">
         <f aca="false">Chạy!M49</f>
@@ -5366,11 +5366,11 @@
       </c>
       <c r="K26" s="16" t="n">
         <f aca="false">J26+L26</f>
-        <v>2.171</v>
+        <v>2.201</v>
       </c>
       <c r="L26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.051</v>
+        <v>0.081</v>
       </c>
       <c r="M26" s="16" t="n">
         <f aca="false">Chạy!O49</f>
@@ -5378,11 +5378,11 @@
       </c>
       <c r="N26" s="16" t="n">
         <f aca="false">M26+O26</f>
-        <v>2.179</v>
+        <v>2.101</v>
       </c>
       <c r="O26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.059</v>
+        <v>-0.019</v>
       </c>
       <c r="P26" s="17"/>
       <c r="Q26" s="18" t="n">
@@ -5406,11 +5406,11 @@
       </c>
       <c r="E27" s="16" t="n">
         <f aca="false">D27+F27</f>
-        <v>2.126</v>
+        <v>2.152</v>
       </c>
       <c r="F27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>-0.004</v>
+        <v>0.022</v>
       </c>
       <c r="G27" s="16" t="n">
         <f aca="false">Chạy!I53</f>
@@ -5418,11 +5418,11 @@
       </c>
       <c r="H27" s="16" t="n">
         <f aca="false">G27+I27</f>
-        <v>2.114</v>
+        <v>2.206</v>
       </c>
       <c r="I27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>-0.016</v>
+        <v>0.076</v>
       </c>
       <c r="J27" s="16" t="n">
         <f aca="false">Chạy!M57</f>
@@ -5430,11 +5430,11 @@
       </c>
       <c r="K27" s="16" t="n">
         <f aca="false">J27+L27</f>
-        <v>2.179</v>
+        <v>2.187</v>
       </c>
       <c r="L27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.049</v>
+        <v>0.057</v>
       </c>
       <c r="M27" s="16" t="n">
         <f aca="false">Chạy!O57</f>
@@ -5442,11 +5442,11 @@
       </c>
       <c r="N27" s="16" t="n">
         <f aca="false">M27+O27</f>
-        <v>2.179</v>
+        <v>2.104</v>
       </c>
       <c r="O27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.049</v>
+        <v>-0.026</v>
       </c>
       <c r="P27" s="17"/>
       <c r="Q27" s="18" t="n">
@@ -5470,11 +5470,11 @@
       </c>
       <c r="E28" s="16" t="n">
         <f aca="false">D28+F28</f>
-        <v>2.225</v>
+        <v>2.124</v>
       </c>
       <c r="F28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.085</v>
+        <v>-0.016</v>
       </c>
       <c r="G28" s="16" t="n">
         <f aca="false">Chạy!I61</f>
@@ -5482,11 +5482,11 @@
       </c>
       <c r="H28" s="16" t="n">
         <f aca="false">G28+I28</f>
-        <v>2.234</v>
+        <v>2.236</v>
       </c>
       <c r="I28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.094</v>
+        <v>0.096</v>
       </c>
       <c r="J28" s="16" t="n">
         <f aca="false">Chạy!M65</f>
@@ -5494,11 +5494,11 @@
       </c>
       <c r="K28" s="16" t="n">
         <f aca="false">J28+L28</f>
-        <v>2.216</v>
+        <v>2.203</v>
       </c>
       <c r="L28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.076</v>
+        <v>0.063</v>
       </c>
       <c r="M28" s="16" t="n">
         <f aca="false">Chạy!O65</f>
@@ -5506,11 +5506,11 @@
       </c>
       <c r="N28" s="16" t="n">
         <f aca="false">M28+O28</f>
-        <v>2.163</v>
+        <v>2.119</v>
       </c>
       <c r="O28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.023</v>
+        <v>-0.021</v>
       </c>
       <c r="P28" s="17"/>
       <c r="Q28" s="18" t="n">
@@ -5534,11 +5534,11 @@
       </c>
       <c r="E29" s="16" t="n">
         <f aca="false">D29+F29</f>
-        <v>2.231</v>
+        <v>2.13</v>
       </c>
       <c r="F29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.091</v>
+        <v>-0.01</v>
       </c>
       <c r="G29" s="16" t="n">
         <f aca="false">Chạy!I69</f>
@@ -5546,11 +5546,11 @@
       </c>
       <c r="H29" s="16" t="n">
         <f aca="false">G29+I29</f>
-        <v>2.178</v>
+        <v>2.174</v>
       </c>
       <c r="I29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.038</v>
+        <v>0.034</v>
       </c>
       <c r="J29" s="16" t="n">
         <f aca="false">Chạy!M73</f>
@@ -5558,11 +5558,11 @@
       </c>
       <c r="K29" s="16" t="n">
         <f aca="false">J29+L29</f>
-        <v>2.162</v>
+        <v>2.235</v>
       </c>
       <c r="L29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.022</v>
+        <v>0.095</v>
       </c>
       <c r="M29" s="16" t="n">
         <f aca="false">Chạy!O73</f>
@@ -5570,11 +5570,11 @@
       </c>
       <c r="N29" s="16" t="n">
         <f aca="false">M29+O29</f>
-        <v>2.121</v>
+        <v>2.144</v>
       </c>
       <c r="O29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>-0.019</v>
+        <v>0.004</v>
       </c>
       <c r="P29" s="17"/>
       <c r="Q29" s="18"/>
@@ -5732,7 +5732,7 @@
     <row r="2" s="26" customFormat="true" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="27" t="str">
         <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,4,0)</f>
-        <v xml:space="preserve">Kèm theo BBNT số: 18.NĐXB6A/CVXD ngày 03 tháng 09 năm 2026</v>
+        <v xml:space="preserve">Kèm theo BBNT số: 18.NĐXB6A/CVXD ngày 06 tháng 09 năm 2026</v>
       </c>
       <c r="B2" s="27"/>
       <c r="C2" s="27"/>
@@ -8621,7 +8621,7 @@
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="str">
         <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,4,0)</f>
-        <v xml:space="preserve">Kèm theo BBNT số: 20.NĐXB6A/CVXD ngày 04 tháng 09 năm 2026</v>
+        <v xml:space="preserve">Kèm theo BBNT số: 20.NĐXB6A/CVXD ngày 07 tháng 09 năm 2026</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -8864,11 +8864,11 @@
       </c>
       <c r="E21" s="16" t="n">
         <f aca="false">D21+F21</f>
-        <v>2.312</v>
+        <v>2.32</v>
       </c>
       <c r="F21" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>-0.028</v>
+        <v>-0.02</v>
       </c>
       <c r="G21" s="16" t="n">
         <f aca="false">Chạy!I4</f>
@@ -8876,11 +8876,11 @@
       </c>
       <c r="H21" s="16" t="n">
         <f aca="false">G21+I21</f>
-        <v>2.415</v>
+        <v>2.419</v>
       </c>
       <c r="I21" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.075</v>
+        <v>0.079</v>
       </c>
       <c r="J21" s="16" t="n">
         <f aca="false">Chạy!M8</f>
@@ -8888,11 +8888,11 @@
       </c>
       <c r="K21" s="16" t="n">
         <f aca="false">J21+L21</f>
-        <v>2.403</v>
+        <v>2.332</v>
       </c>
       <c r="L21" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.063</v>
+        <v>-0.008</v>
       </c>
       <c r="M21" s="16" t="n">
         <f aca="false">Chạy!O8</f>
@@ -8900,11 +8900,11 @@
       </c>
       <c r="N21" s="16" t="n">
         <f aca="false">M21+O21</f>
-        <v>2.414</v>
+        <v>2.418</v>
       </c>
       <c r="O21" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.074</v>
+        <v>0.078</v>
       </c>
       <c r="P21" s="17"/>
       <c r="Q21" s="18" t="n">
@@ -8928,11 +8928,11 @@
       </c>
       <c r="E22" s="16" t="n">
         <f aca="false">D22+F22</f>
-        <v>2.318</v>
+        <v>2.415</v>
       </c>
       <c r="F22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>-0.022</v>
+        <v>0.075</v>
       </c>
       <c r="G22" s="16" t="n">
         <f aca="false">Chạy!I12</f>
@@ -8940,11 +8940,11 @@
       </c>
       <c r="H22" s="16" t="n">
         <f aca="false">G22+I22</f>
-        <v>2.325</v>
+        <v>2.403</v>
       </c>
       <c r="I22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>-0.015</v>
+        <v>0.063</v>
       </c>
       <c r="J22" s="16" t="n">
         <f aca="false">Chạy!M16</f>
@@ -8952,11 +8952,11 @@
       </c>
       <c r="K22" s="16" t="n">
         <f aca="false">J22+L22</f>
-        <v>2.434</v>
+        <v>2.423</v>
       </c>
       <c r="L22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.094</v>
+        <v>0.083</v>
       </c>
       <c r="M22" s="16" t="n">
         <f aca="false">Chạy!O16</f>
@@ -8964,11 +8964,11 @@
       </c>
       <c r="N22" s="16" t="n">
         <f aca="false">M22+O22</f>
-        <v>2.399</v>
+        <v>2.38</v>
       </c>
       <c r="O22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.059</v>
+        <v>0.04</v>
       </c>
       <c r="P22" s="17"/>
       <c r="Q22" s="18" t="n">
@@ -8992,11 +8992,11 @@
       </c>
       <c r="E23" s="16" t="n">
         <f aca="false">D23+F23</f>
-        <v>2.377</v>
+        <v>2.387</v>
       </c>
       <c r="F23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.027</v>
+        <v>0.037</v>
       </c>
       <c r="G23" s="16" t="n">
         <f aca="false">Chạy!I20</f>
@@ -9004,11 +9004,11 @@
       </c>
       <c r="H23" s="16" t="n">
         <f aca="false">G23+I23</f>
-        <v>2.45</v>
+        <v>2.441</v>
       </c>
       <c r="I23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.1</v>
+        <v>0.091</v>
       </c>
       <c r="J23" s="16" t="n">
         <f aca="false">Chạy!M24</f>
@@ -9016,11 +9016,11 @@
       </c>
       <c r="K23" s="16" t="n">
         <f aca="false">J23+L23</f>
-        <v>2.326</v>
+        <v>2.424</v>
       </c>
       <c r="L23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>-0.024</v>
+        <v>0.074</v>
       </c>
       <c r="M23" s="16" t="n">
         <f aca="false">Chạy!O24</f>
@@ -9028,11 +9028,11 @@
       </c>
       <c r="N23" s="16" t="n">
         <f aca="false">M23+O23</f>
-        <v>2.355</v>
+        <v>2.442</v>
       </c>
       <c r="O23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.005</v>
+        <v>0.092</v>
       </c>
       <c r="P23" s="17"/>
       <c r="Q23" s="18" t="n">
@@ -9056,11 +9056,11 @@
       </c>
       <c r="E24" s="16" t="n">
         <f aca="false">D24+F24</f>
-        <v>2.414</v>
+        <v>2.373</v>
       </c>
       <c r="F24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.054</v>
+        <v>0.013</v>
       </c>
       <c r="G24" s="16" t="n">
         <f aca="false">Chạy!I28</f>
@@ -9068,11 +9068,11 @@
       </c>
       <c r="H24" s="16" t="n">
         <f aca="false">G24+I24</f>
-        <v>2.404</v>
+        <v>2.331</v>
       </c>
       <c r="I24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.044</v>
+        <v>-0.029</v>
       </c>
       <c r="J24" s="16" t="n">
         <f aca="false">Chạy!M32</f>
@@ -9080,11 +9080,11 @@
       </c>
       <c r="K24" s="16" t="n">
         <f aca="false">J24+L24</f>
-        <v>2.42</v>
+        <v>2.378</v>
       </c>
       <c r="L24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.06</v>
+        <v>0.018</v>
       </c>
       <c r="M24" s="16" t="n">
         <f aca="false">Chạy!O32</f>
@@ -9092,11 +9092,11 @@
       </c>
       <c r="N24" s="16" t="n">
         <f aca="false">M24+O24</f>
-        <v>2.359</v>
+        <v>2.44</v>
       </c>
       <c r="O24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>-0.001</v>
+        <v>0.08</v>
       </c>
       <c r="P24" s="17"/>
       <c r="Q24" s="18" t="n">
@@ -9120,11 +9120,11 @@
       </c>
       <c r="E25" s="16" t="n">
         <f aca="false">D25+F25</f>
-        <v>2.389</v>
+        <v>2.426</v>
       </c>
       <c r="F25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.029</v>
+        <v>0.066</v>
       </c>
       <c r="G25" s="16" t="n">
         <f aca="false">Chạy!I36</f>
@@ -9132,11 +9132,11 @@
       </c>
       <c r="H25" s="16" t="n">
         <f aca="false">G25+I25</f>
-        <v>2.441</v>
+        <v>2.453</v>
       </c>
       <c r="I25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.081</v>
+        <v>0.093</v>
       </c>
       <c r="J25" s="16" t="n">
         <f aca="false">Chạy!M40</f>
@@ -9144,11 +9144,11 @@
       </c>
       <c r="K25" s="16" t="n">
         <f aca="false">J25+L25</f>
-        <v>2.392</v>
+        <v>2.344</v>
       </c>
       <c r="L25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.032</v>
+        <v>-0.016</v>
       </c>
       <c r="M25" s="16" t="n">
         <f aca="false">Chạy!O40</f>
@@ -9156,11 +9156,11 @@
       </c>
       <c r="N25" s="16" t="n">
         <f aca="false">M25+O25</f>
-        <v>2.393</v>
+        <v>2.349</v>
       </c>
       <c r="O25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.033</v>
+        <v>-0.011</v>
       </c>
       <c r="P25" s="17"/>
       <c r="Q25" s="18" t="n">
@@ -9184,11 +9184,11 @@
       </c>
       <c r="E26" s="16" t="n">
         <f aca="false">D26+F26</f>
-        <v>2.436</v>
+        <v>2.418</v>
       </c>
       <c r="F26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.066</v>
+        <v>0.048</v>
       </c>
       <c r="G26" s="16" t="n">
         <f aca="false">Chạy!I44</f>
@@ -9196,11 +9196,11 @@
       </c>
       <c r="H26" s="16" t="n">
         <f aca="false">G26+I26</f>
-        <v>2.448</v>
+        <v>2.463</v>
       </c>
       <c r="I26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.078</v>
+        <v>0.093</v>
       </c>
       <c r="J26" s="16" t="n">
         <f aca="false">Chạy!M48</f>
@@ -9208,11 +9208,11 @@
       </c>
       <c r="K26" s="16" t="n">
         <f aca="false">J26+L26</f>
-        <v>2.413</v>
+        <v>2.393</v>
       </c>
       <c r="L26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.043</v>
+        <v>0.023</v>
       </c>
       <c r="M26" s="16" t="n">
         <f aca="false">Chạy!O48</f>
@@ -9220,11 +9220,11 @@
       </c>
       <c r="N26" s="16" t="n">
         <f aca="false">M26+O26</f>
-        <v>2.404</v>
+        <v>2.465</v>
       </c>
       <c r="O26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.034</v>
+        <v>0.095</v>
       </c>
       <c r="P26" s="17"/>
       <c r="Q26" s="18" t="n">
@@ -9248,11 +9248,11 @@
       </c>
       <c r="E27" s="16" t="n">
         <f aca="false">D27+F27</f>
-        <v>2.385</v>
+        <v>2.474</v>
       </c>
       <c r="F27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.005</v>
+        <v>0.094</v>
       </c>
       <c r="G27" s="16" t="n">
         <f aca="false">Chạy!I52</f>
@@ -9260,11 +9260,11 @@
       </c>
       <c r="H27" s="16" t="n">
         <f aca="false">G27+I27</f>
-        <v>2.48</v>
+        <v>2.418</v>
       </c>
       <c r="I27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.1</v>
+        <v>0.038</v>
       </c>
       <c r="J27" s="16" t="n">
         <f aca="false">Chạy!M56</f>
@@ -9272,11 +9272,11 @@
       </c>
       <c r="K27" s="16" t="n">
         <f aca="false">J27+L27</f>
-        <v>2.422</v>
+        <v>2.44</v>
       </c>
       <c r="L27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.042</v>
+        <v>0.06</v>
       </c>
       <c r="M27" s="16" t="n">
         <f aca="false">Chạy!O56</f>
@@ -9284,11 +9284,11 @@
       </c>
       <c r="N27" s="16" t="n">
         <f aca="false">M27+O27</f>
-        <v>2.48</v>
+        <v>2.426</v>
       </c>
       <c r="O27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.1</v>
+        <v>0.046</v>
       </c>
       <c r="P27" s="17"/>
       <c r="Q27" s="18" t="n">
@@ -9312,11 +9312,11 @@
       </c>
       <c r="E28" s="16" t="n">
         <f aca="false">D28+F28</f>
-        <v>2.411</v>
+        <v>2.445</v>
       </c>
       <c r="F28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.021</v>
+        <v>0.055</v>
       </c>
       <c r="G28" s="16" t="n">
         <f aca="false">Chạy!I60</f>
@@ -9324,11 +9324,11 @@
       </c>
       <c r="H28" s="16" t="n">
         <f aca="false">G28+I28</f>
-        <v>2.388</v>
+        <v>2.399</v>
       </c>
       <c r="I28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>-0.002</v>
+        <v>0.009</v>
       </c>
       <c r="J28" s="16" t="n">
         <f aca="false">Chạy!M64</f>
@@ -9336,11 +9336,11 @@
       </c>
       <c r="K28" s="16" t="n">
         <f aca="false">J28+L28</f>
-        <v>2.423</v>
+        <v>2.371</v>
       </c>
       <c r="L28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.033</v>
+        <v>-0.019</v>
       </c>
       <c r="M28" s="16" t="n">
         <f aca="false">Chạy!O64</f>
@@ -9348,11 +9348,11 @@
       </c>
       <c r="N28" s="16" t="n">
         <f aca="false">M28+O28</f>
-        <v>2.448</v>
+        <v>2.396</v>
       </c>
       <c r="O28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.058</v>
+        <v>0.006</v>
       </c>
       <c r="P28" s="17"/>
       <c r="Q28" s="18" t="n">
@@ -9376,11 +9376,11 @@
       </c>
       <c r="E29" s="16" t="n">
         <f aca="false">D29+F29</f>
-        <v>2.48</v>
+        <v>2.414</v>
       </c>
       <c r="F29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.09</v>
+        <v>0.024</v>
       </c>
       <c r="G29" s="16" t="n">
         <f aca="false">Chạy!I68</f>
@@ -9388,11 +9388,11 @@
       </c>
       <c r="H29" s="16" t="n">
         <f aca="false">G29+I29</f>
-        <v>2.371</v>
+        <v>2.456</v>
       </c>
       <c r="I29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>-0.019</v>
+        <v>0.066</v>
       </c>
       <c r="J29" s="16" t="n">
         <f aca="false">Chạy!M72</f>
@@ -9400,11 +9400,11 @@
       </c>
       <c r="K29" s="16" t="n">
         <f aca="false">J29+L29</f>
-        <v>2.471</v>
+        <v>2.424</v>
       </c>
       <c r="L29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.081</v>
+        <v>0.034</v>
       </c>
       <c r="M29" s="16" t="n">
         <f aca="false">Chạy!O72</f>
@@ -9412,11 +9412,11 @@
       </c>
       <c r="N29" s="16" t="n">
         <f aca="false">M29+O29</f>
-        <v>2.386</v>
+        <v>2.362</v>
       </c>
       <c r="O29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>-0.004</v>
+        <v>-0.028</v>
       </c>
       <c r="P29" s="17"/>
       <c r="Q29" s="18"/>
@@ -9575,7 +9575,7 @@
     <row r="2" s="26" customFormat="true" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="27" t="str">
         <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,4,0)</f>
-        <v xml:space="preserve">Kèm theo BBNT số: 20.NĐXB6A/CVXD ngày 04 tháng 09 năm 2026</v>
+        <v xml:space="preserve">Kèm theo BBNT số: 20.NĐXB6A/CVXD ngày 07 tháng 09 năm 2026</v>
       </c>
       <c r="B2" s="27"/>
       <c r="C2" s="27"/>
@@ -13070,7 +13070,7 @@
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="str">
         <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,4,0)</f>
-        <v xml:space="preserve">Kèm theo BBNT số: 22.NĐXB6A/CVXD ngày 05 tháng 09 năm 2026</v>
+        <v xml:space="preserve">Kèm theo BBNT số: 22.NĐXB6A/CVXD ngày 08 tháng 09 năm 2026</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -13304,11 +13304,11 @@
       </c>
       <c r="E21" s="16" t="n">
         <f aca="false">D21+F21</f>
-        <v>2.533</v>
+        <v>2.562</v>
       </c>
       <c r="F21" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.013</v>
+        <v>0.042</v>
       </c>
       <c r="G21" s="16" t="n">
         <f aca="false">Chạy!I3</f>
@@ -13316,11 +13316,11 @@
       </c>
       <c r="H21" s="16" t="n">
         <f aca="false">G21+I21</f>
-        <v>2.575</v>
+        <v>2.553</v>
       </c>
       <c r="I21" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.055</v>
+        <v>0.033</v>
       </c>
       <c r="J21" s="16" t="n">
         <f aca="false">Chạy!M7</f>
@@ -13328,11 +13328,11 @@
       </c>
       <c r="K21" s="16" t="n">
         <f aca="false">J21+L21</f>
-        <v>2.518</v>
+        <v>2.535</v>
       </c>
       <c r="L21" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>-0.002</v>
+        <v>0.015</v>
       </c>
       <c r="M21" s="16" t="n">
         <f aca="false">Chạy!O7</f>
@@ -13340,11 +13340,11 @@
       </c>
       <c r="N21" s="16" t="n">
         <f aca="false">M21+O21</f>
-        <v>2.579</v>
+        <v>2.58</v>
       </c>
       <c r="O21" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.059</v>
+        <v>0.06</v>
       </c>
       <c r="P21" s="17"/>
       <c r="Q21" s="18" t="n">
@@ -13368,11 +13368,11 @@
       </c>
       <c r="E22" s="16" t="n">
         <f aca="false">D22+F22</f>
-        <v>2.543</v>
+        <v>2.558</v>
       </c>
       <c r="F22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.023</v>
+        <v>0.038</v>
       </c>
       <c r="G22" s="16" t="n">
         <f aca="false">Chạy!I11</f>
@@ -13380,11 +13380,11 @@
       </c>
       <c r="H22" s="16" t="n">
         <f aca="false">G22+I22</f>
-        <v>2.495</v>
+        <v>2.501</v>
       </c>
       <c r="I22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>-0.025</v>
+        <v>-0.019</v>
       </c>
       <c r="J22" s="16" t="n">
         <f aca="false">Chạy!M15</f>
@@ -13392,11 +13392,11 @@
       </c>
       <c r="K22" s="16" t="n">
         <f aca="false">J22+L22</f>
-        <v>2.531</v>
+        <v>2.558</v>
       </c>
       <c r="L22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.011</v>
+        <v>0.038</v>
       </c>
       <c r="M22" s="16" t="n">
         <f aca="false">Chạy!O15</f>
@@ -13404,11 +13404,11 @@
       </c>
       <c r="N22" s="16" t="n">
         <f aca="false">M22+O22</f>
-        <v>2.569</v>
+        <v>2.505</v>
       </c>
       <c r="O22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.049</v>
+        <v>-0.015</v>
       </c>
       <c r="P22" s="17"/>
       <c r="Q22" s="18" t="n">
@@ -13432,11 +13432,11 @@
       </c>
       <c r="E23" s="16" t="n">
         <f aca="false">D23+F23</f>
-        <v>2.6</v>
+        <v>2.576</v>
       </c>
       <c r="F23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.07</v>
+        <v>0.046</v>
       </c>
       <c r="G23" s="16" t="n">
         <f aca="false">Chạy!I19</f>
@@ -13444,11 +13444,11 @@
       </c>
       <c r="H23" s="16" t="n">
         <f aca="false">G23+I23</f>
-        <v>2.504</v>
+        <v>2.609</v>
       </c>
       <c r="I23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>-0.026</v>
+        <v>0.079</v>
       </c>
       <c r="J23" s="16" t="n">
         <f aca="false">Chạy!M23</f>
@@ -13456,11 +13456,11 @@
       </c>
       <c r="K23" s="16" t="n">
         <f aca="false">J23+L23</f>
-        <v>2.513</v>
+        <v>2.615</v>
       </c>
       <c r="L23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>-0.017</v>
+        <v>0.085</v>
       </c>
       <c r="M23" s="16" t="n">
         <f aca="false">Chạy!O23</f>
@@ -13468,11 +13468,11 @@
       </c>
       <c r="N23" s="16" t="n">
         <f aca="false">M23+O23</f>
-        <v>2.548</v>
+        <v>2.582</v>
       </c>
       <c r="O23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.018</v>
+        <v>0.052</v>
       </c>
       <c r="P23" s="17"/>
       <c r="Q23" s="18" t="n">
@@ -13496,11 +13496,11 @@
       </c>
       <c r="E24" s="16" t="n">
         <f aca="false">D24+F24</f>
-        <v>2.513</v>
+        <v>2.575</v>
       </c>
       <c r="F24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>-0.027</v>
+        <v>0.035</v>
       </c>
       <c r="G24" s="16" t="n">
         <f aca="false">Chạy!I27</f>
@@ -13508,11 +13508,11 @@
       </c>
       <c r="H24" s="16" t="n">
         <f aca="false">G24+I24</f>
-        <v>2.554</v>
+        <v>2.585</v>
       </c>
       <c r="I24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.014</v>
+        <v>0.045</v>
       </c>
       <c r="J24" s="16" t="n">
         <f aca="false">Chạy!M31</f>
@@ -13520,11 +13520,11 @@
       </c>
       <c r="K24" s="16" t="n">
         <f aca="false">J24+L24</f>
-        <v>2.611</v>
+        <v>2.573</v>
       </c>
       <c r="L24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.071</v>
+        <v>0.033</v>
       </c>
       <c r="M24" s="16" t="n">
         <f aca="false">Chạy!O31</f>
@@ -13532,11 +13532,11 @@
       </c>
       <c r="N24" s="16" t="n">
         <f aca="false">M24+O24</f>
-        <v>2.514</v>
+        <v>2.574</v>
       </c>
       <c r="O24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>-0.026</v>
+        <v>0.034</v>
       </c>
       <c r="P24" s="17"/>
       <c r="Q24" s="18" t="n">
@@ -13560,11 +13560,11 @@
       </c>
       <c r="E25" s="16" t="n">
         <f aca="false">D25+F25</f>
-        <v>2.585</v>
+        <v>2.547</v>
       </c>
       <c r="F25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.045</v>
+        <v>0.007</v>
       </c>
       <c r="G25" s="16" t="n">
         <f aca="false">Chạy!I35</f>
@@ -13572,11 +13572,11 @@
       </c>
       <c r="H25" s="16" t="n">
         <f aca="false">G25+I25</f>
-        <v>2.516</v>
+        <v>2.619</v>
       </c>
       <c r="I25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>-0.024</v>
+        <v>0.079</v>
       </c>
       <c r="J25" s="16" t="n">
         <f aca="false">Chạy!M39</f>
@@ -13584,11 +13584,11 @@
       </c>
       <c r="K25" s="16" t="n">
         <f aca="false">J25+L25</f>
-        <v>2.516</v>
+        <v>2.565</v>
       </c>
       <c r="L25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>-0.024</v>
+        <v>0.025</v>
       </c>
       <c r="M25" s="16" t="n">
         <f aca="false">Chạy!O39</f>
@@ -13596,11 +13596,11 @@
       </c>
       <c r="N25" s="16" t="n">
         <f aca="false">M25+O25</f>
-        <v>2.51</v>
+        <v>2.633</v>
       </c>
       <c r="O25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>-0.03</v>
+        <v>0.093</v>
       </c>
       <c r="P25" s="17"/>
       <c r="Q25" s="18" t="n">
@@ -13624,11 +13624,11 @@
       </c>
       <c r="E26" s="16" t="n">
         <f aca="false">D26+F26</f>
-        <v>2.534</v>
+        <v>2.606</v>
       </c>
       <c r="F26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>-0.016</v>
+        <v>0.056</v>
       </c>
       <c r="G26" s="16" t="n">
         <f aca="false">Chạy!I43</f>
@@ -13636,11 +13636,11 @@
       </c>
       <c r="H26" s="16" t="n">
         <f aca="false">G26+I26</f>
-        <v>2.617</v>
+        <v>2.611</v>
       </c>
       <c r="I26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.067</v>
+        <v>0.061</v>
       </c>
       <c r="J26" s="16" t="n">
         <f aca="false">Chạy!M47</f>
@@ -13648,11 +13648,11 @@
       </c>
       <c r="K26" s="16" t="n">
         <f aca="false">J26+L26</f>
-        <v>2.557</v>
+        <v>2.619</v>
       </c>
       <c r="L26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.007</v>
+        <v>0.069</v>
       </c>
       <c r="M26" s="16" t="n">
         <f aca="false">Chạy!O47</f>
@@ -13660,11 +13660,11 @@
       </c>
       <c r="N26" s="16" t="n">
         <f aca="false">M26+O26</f>
-        <v>2.559</v>
+        <v>2.581</v>
       </c>
       <c r="O26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.009</v>
+        <v>0.031</v>
       </c>
       <c r="P26" s="17"/>
       <c r="Q26" s="18" t="n">
@@ -13688,11 +13688,11 @@
       </c>
       <c r="E27" s="16" t="n">
         <f aca="false">D27+F27</f>
-        <v>2.533</v>
+        <v>2.534</v>
       </c>
       <c r="F27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>-0.027</v>
+        <v>-0.026</v>
       </c>
       <c r="G27" s="16" t="n">
         <f aca="false">Chạy!I51</f>
@@ -13700,11 +13700,11 @@
       </c>
       <c r="H27" s="16" t="n">
         <f aca="false">G27+I27</f>
-        <v>2.545</v>
+        <v>2.578</v>
       </c>
       <c r="I27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>-0.015</v>
+        <v>0.018</v>
       </c>
       <c r="J27" s="16" t="n">
         <f aca="false">Chạy!M55</f>
@@ -13712,11 +13712,11 @@
       </c>
       <c r="K27" s="16" t="n">
         <f aca="false">J27+L27</f>
-        <v>2.538</v>
+        <v>2.651</v>
       </c>
       <c r="L27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>-0.022</v>
+        <v>0.091</v>
       </c>
       <c r="M27" s="16" t="n">
         <f aca="false">Chạy!O55</f>
@@ -13724,11 +13724,11 @@
       </c>
       <c r="N27" s="16" t="n">
         <f aca="false">M27+O27</f>
-        <v>2.604</v>
+        <v>2.603</v>
       </c>
       <c r="O27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.044</v>
+        <v>0.043</v>
       </c>
       <c r="P27" s="17"/>
       <c r="Q27" s="18" t="n">
@@ -13752,11 +13752,11 @@
       </c>
       <c r="E28" s="16" t="n">
         <f aca="false">D28+F28</f>
-        <v>2.571</v>
+        <v>2.637</v>
       </c>
       <c r="F28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.001</v>
+        <v>0.067</v>
       </c>
       <c r="G28" s="16" t="n">
         <f aca="false">Chạy!I59</f>
@@ -13764,11 +13764,11 @@
       </c>
       <c r="H28" s="16" t="n">
         <f aca="false">G28+I28</f>
-        <v>2.609</v>
+        <v>2.625</v>
       </c>
       <c r="I28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.039</v>
+        <v>0.055</v>
       </c>
       <c r="J28" s="16" t="n">
         <f aca="false">Chạy!M63</f>
@@ -13776,11 +13776,11 @@
       </c>
       <c r="K28" s="16" t="n">
         <f aca="false">J28+L28</f>
-        <v>2.584</v>
+        <v>2.58</v>
       </c>
       <c r="L28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.014</v>
+        <v>0.01</v>
       </c>
       <c r="M28" s="16" t="n">
         <f aca="false">Chạy!O63</f>
@@ -13788,11 +13788,11 @@
       </c>
       <c r="N28" s="16" t="n">
         <f aca="false">M28+O28</f>
-        <v>2.666</v>
+        <v>2.604</v>
       </c>
       <c r="O28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.096</v>
+        <v>0.034</v>
       </c>
       <c r="P28" s="17"/>
       <c r="Q28" s="18" t="n">
@@ -13816,11 +13816,11 @@
       </c>
       <c r="E29" s="16" t="n">
         <f aca="false">D29+F29</f>
-        <v>2.598</v>
+        <v>2.589</v>
       </c>
       <c r="F29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.028</v>
+        <v>0.019</v>
       </c>
       <c r="G29" s="16" t="n">
         <f aca="false">Chạy!I67</f>
@@ -13828,11 +13828,11 @@
       </c>
       <c r="H29" s="16" t="n">
         <f aca="false">G29+I29</f>
-        <v>2.608</v>
+        <v>2.56</v>
       </c>
       <c r="I29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.038</v>
+        <v>-0.01</v>
       </c>
       <c r="J29" s="16" t="n">
         <f aca="false">Chạy!M71</f>
@@ -13840,11 +13840,11 @@
       </c>
       <c r="K29" s="16" t="n">
         <f aca="false">J29+L29</f>
-        <v>2.602</v>
+        <v>2.54</v>
       </c>
       <c r="L29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.032</v>
+        <v>-0.03</v>
       </c>
       <c r="M29" s="16" t="n">
         <f aca="false">Chạy!O71</f>
@@ -13852,11 +13852,11 @@
       </c>
       <c r="N29" s="16" t="n">
         <f aca="false">M29+O29</f>
-        <v>2.575</v>
+        <v>2.568</v>
       </c>
       <c r="O29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.005</v>
+        <v>-0.002</v>
       </c>
       <c r="P29" s="17"/>
       <c r="Q29" s="18"/>
@@ -14015,7 +14015,7 @@
     <row r="2" s="70" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="27" t="str">
         <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,4,0)</f>
-        <v xml:space="preserve">Kèm theo BBNT số: 22.NĐXB6A/CVXD ngày 05 tháng 09 năm 2026</v>
+        <v xml:space="preserve">Kèm theo BBNT số: 22.NĐXB6A/CVXD ngày 08 tháng 09 năm 2026</v>
       </c>
       <c r="B2" s="27"/>
       <c r="C2" s="27"/>
@@ -16881,7 +16881,7 @@
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="74" t="str">
         <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,4,0)</f>
-        <v xml:space="preserve">Kèm theo BBNT số: 23.NĐXB6A/CVXD ngày 06 tháng 09 năm 2026</v>
+        <v xml:space="preserve">Kèm theo BBNT số: 23.NĐXB6A/CVXD ngày 09 tháng 09 năm 2026</v>
       </c>
       <c r="B2" s="74"/>
       <c r="C2" s="74"/>
@@ -17115,11 +17115,11 @@
       </c>
       <c r="E20" s="16" t="n">
         <f aca="false">D20+F20</f>
-        <v>2.924</v>
+        <v>2.835</v>
       </c>
       <c r="F20" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.064</v>
+        <v>-0.025</v>
       </c>
       <c r="G20" s="16" t="n">
         <f aca="false">Chạy!I2</f>
@@ -17127,11 +17127,11 @@
       </c>
       <c r="H20" s="16" t="n">
         <f aca="false">G20+I20</f>
-        <v>2.599</v>
+        <v>2.583</v>
       </c>
       <c r="I20" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.019</v>
+        <v>0.003</v>
       </c>
       <c r="J20" s="16" t="n">
         <f aca="false">Chạy!M6</f>
@@ -17139,11 +17139,11 @@
       </c>
       <c r="K20" s="16" t="n">
         <f aca="false">J20+L20</f>
-        <v>2.824</v>
+        <v>2.844</v>
       </c>
       <c r="L20" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.054</v>
+        <v>0.074</v>
       </c>
       <c r="M20" s="16" t="n">
         <f aca="false">Chạy!O6</f>
@@ -17151,11 +17151,11 @@
       </c>
       <c r="N20" s="16" t="n">
         <f aca="false">M20+O20</f>
-        <v>2.792</v>
+        <v>2.84</v>
       </c>
       <c r="O20" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.022</v>
+        <v>0.07</v>
       </c>
       <c r="P20" s="17"/>
       <c r="Q20" s="18" t="n">
@@ -17179,11 +17179,11 @@
       </c>
       <c r="E21" s="16" t="n">
         <f aca="false">D21+F21</f>
-        <v>2.955</v>
+        <v>2.874</v>
       </c>
       <c r="F21" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.095</v>
+        <v>0.014</v>
       </c>
       <c r="G21" s="16" t="n">
         <f aca="false">Chạy!I10</f>
@@ -17191,11 +17191,11 @@
       </c>
       <c r="H21" s="16" t="n">
         <f aca="false">G21+I21</f>
-        <v>2.66</v>
+        <v>2.677</v>
       </c>
       <c r="I21" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.08</v>
+        <v>0.097</v>
       </c>
       <c r="J21" s="16" t="n">
         <f aca="false">Chạy!M14</f>
@@ -17203,11 +17203,11 @@
       </c>
       <c r="K21" s="16" t="n">
         <f aca="false">J21+L21</f>
-        <v>2.757</v>
+        <v>2.743</v>
       </c>
       <c r="L21" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>-0.013</v>
+        <v>-0.027</v>
       </c>
       <c r="M21" s="16" t="n">
         <f aca="false">Chạy!O14</f>
@@ -17215,11 +17215,11 @@
       </c>
       <c r="N21" s="16" t="n">
         <f aca="false">M21+O21</f>
-        <v>2.765</v>
+        <v>2.82</v>
       </c>
       <c r="O21" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>-0.005</v>
+        <v>0.05</v>
       </c>
       <c r="P21" s="17"/>
       <c r="Q21" s="18" t="n">
@@ -17243,11 +17243,11 @@
       </c>
       <c r="E22" s="16" t="n">
         <f aca="false">D22+F22</f>
-        <v>2.871</v>
+        <v>2.91</v>
       </c>
       <c r="F22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.001</v>
+        <v>0.04</v>
       </c>
       <c r="G22" s="16" t="n">
         <f aca="false">Chạy!I18</f>
@@ -17255,11 +17255,11 @@
       </c>
       <c r="H22" s="16" t="n">
         <f aca="false">G22+I22</f>
-        <v>2.65</v>
+        <v>2.612</v>
       </c>
       <c r="I22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.06</v>
+        <v>0.022</v>
       </c>
       <c r="J22" s="16" t="n">
         <f aca="false">Chạy!M22</f>
@@ -17267,11 +17267,11 @@
       </c>
       <c r="K22" s="16" t="n">
         <f aca="false">J22+L22</f>
-        <v>2.807</v>
+        <v>2.835</v>
       </c>
       <c r="L22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.027</v>
+        <v>0.055</v>
       </c>
       <c r="M22" s="16" t="n">
         <f aca="false">Chạy!O22</f>
@@ -17279,11 +17279,11 @@
       </c>
       <c r="N22" s="16" t="n">
         <f aca="false">M22+O22</f>
-        <v>2.788</v>
+        <v>2.744</v>
       </c>
       <c r="O22" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.018</v>
+        <v>-0.026</v>
       </c>
       <c r="P22" s="17"/>
       <c r="Q22" s="18" t="n">
@@ -17307,11 +17307,11 @@
       </c>
       <c r="E23" s="16" t="n">
         <f aca="false">D23+F23</f>
-        <v>2.938</v>
+        <v>2.89</v>
       </c>
       <c r="F23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.058</v>
+        <v>0.01</v>
       </c>
       <c r="G23" s="16" t="n">
         <f aca="false">Chạy!I26</f>
@@ -17319,11 +17319,11 @@
       </c>
       <c r="H23" s="16" t="n">
         <f aca="false">G23+I23</f>
-        <v>2.616</v>
+        <v>2.578</v>
       </c>
       <c r="I23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.016</v>
+        <v>-0.022</v>
       </c>
       <c r="J23" s="16" t="n">
         <f aca="false">Chạy!M30</f>
@@ -17331,11 +17331,11 @@
       </c>
       <c r="K23" s="16" t="n">
         <f aca="false">J23+L23</f>
-        <v>2.803</v>
+        <v>2.795</v>
       </c>
       <c r="L23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.013</v>
+        <v>0.005</v>
       </c>
       <c r="M23" s="16" t="n">
         <f aca="false">Chạy!O30</f>
@@ -17343,11 +17343,11 @@
       </c>
       <c r="N23" s="16" t="n">
         <f aca="false">M23+O23</f>
-        <v>2.826</v>
+        <v>2.781</v>
       </c>
       <c r="O23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.046</v>
+        <v>0.001</v>
       </c>
       <c r="P23" s="17"/>
       <c r="Q23" s="18" t="n">
@@ -17371,11 +17371,11 @@
       </c>
       <c r="E24" s="16" t="n">
         <f aca="false">D24+F24</f>
-        <v>2.973</v>
+        <v>2.9</v>
       </c>
       <c r="F24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.093</v>
+        <v>0.02</v>
       </c>
       <c r="G24" s="16" t="n">
         <f aca="false">Chạy!I34</f>
@@ -17383,11 +17383,11 @@
       </c>
       <c r="H24" s="16" t="n">
         <f aca="false">G24+I24</f>
-        <v>2.694</v>
+        <v>2.612</v>
       </c>
       <c r="I24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.094</v>
+        <v>0.012</v>
       </c>
       <c r="J24" s="16" t="n">
         <f aca="false">Chạy!M38</f>
@@ -17395,11 +17395,11 @@
       </c>
       <c r="K24" s="16" t="n">
         <f aca="false">J24+L24</f>
-        <v>2.811</v>
+        <v>2.883</v>
       </c>
       <c r="L24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.021</v>
+        <v>0.093</v>
       </c>
       <c r="M24" s="16" t="n">
         <f aca="false">Chạy!O38</f>
@@ -17407,11 +17407,11 @@
       </c>
       <c r="N24" s="16" t="n">
         <f aca="false">M24+O24</f>
-        <v>2.886</v>
+        <v>2.842</v>
       </c>
       <c r="O24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.096</v>
+        <v>0.052</v>
       </c>
       <c r="P24" s="17"/>
       <c r="Q24" s="18" t="n">
@@ -17435,11 +17435,11 @@
       </c>
       <c r="E25" s="16" t="n">
         <f aca="false">D25+F25</f>
-        <v>2.878</v>
+        <v>2.929</v>
       </c>
       <c r="F25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>-0.012</v>
+        <v>0.039</v>
       </c>
       <c r="G25" s="16" t="n">
         <f aca="false">Chạy!I42</f>
@@ -17447,11 +17447,11 @@
       </c>
       <c r="H25" s="16" t="n">
         <f aca="false">G25+I25</f>
-        <v>2.61</v>
+        <v>2.658</v>
       </c>
       <c r="I25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="J25" s="16" t="n">
         <f aca="false">Chạy!M46</f>
@@ -17459,11 +17459,11 @@
       </c>
       <c r="K25" s="16" t="n">
         <f aca="false">J25+L25</f>
-        <v>2.835</v>
+        <v>2.85</v>
       </c>
       <c r="L25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.035</v>
+        <v>0.05</v>
       </c>
       <c r="M25" s="16" t="n">
         <f aca="false">Chạy!O46</f>
@@ -17471,11 +17471,11 @@
       </c>
       <c r="N25" s="16" t="n">
         <f aca="false">M25+O25</f>
-        <v>2.8</v>
+        <v>2.794</v>
       </c>
       <c r="O25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.01</v>
+        <v>0.004</v>
       </c>
       <c r="P25" s="17"/>
       <c r="Q25" s="18" t="n">
@@ -17499,11 +17499,11 @@
       </c>
       <c r="E26" s="16" t="n">
         <f aca="false">D26+F26</f>
-        <v>2.933</v>
+        <v>2.908</v>
       </c>
       <c r="F26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.033</v>
+        <v>0.008</v>
       </c>
       <c r="G26" s="16" t="n">
         <f aca="false">Chạy!I50</f>
@@ -17511,11 +17511,11 @@
       </c>
       <c r="H26" s="16" t="n">
         <f aca="false">G26+I26</f>
-        <v>2.656</v>
+        <v>2.646</v>
       </c>
       <c r="I26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.036</v>
+        <v>0.026</v>
       </c>
       <c r="J26" s="16" t="n">
         <f aca="false">Chạy!M54</f>
@@ -17523,11 +17523,11 @@
       </c>
       <c r="K26" s="16" t="n">
         <f aca="false">J26+L26</f>
-        <v>2.908</v>
+        <v>2.86</v>
       </c>
       <c r="L26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.098</v>
+        <v>0.05</v>
       </c>
       <c r="M26" s="16" t="n">
         <f aca="false">Chạy!O54</f>
@@ -17535,11 +17535,11 @@
       </c>
       <c r="N26" s="16" t="n">
         <f aca="false">M26+O26</f>
-        <v>2.809</v>
+        <v>2.803</v>
       </c>
       <c r="O26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.009</v>
+        <v>0.003</v>
       </c>
       <c r="P26" s="17"/>
       <c r="Q26" s="18" t="n">
@@ -17563,11 +17563,11 @@
       </c>
       <c r="E27" s="16" t="n">
         <f aca="false">D27+F27</f>
-        <v>2.922</v>
+        <v>2.884</v>
       </c>
       <c r="F27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.012</v>
+        <v>-0.026</v>
       </c>
       <c r="G27" s="16" t="n">
         <f aca="false">Chạy!I58</f>
@@ -17575,11 +17575,11 @@
       </c>
       <c r="H27" s="16" t="n">
         <f aca="false">G27+I27</f>
-        <v>2.719</v>
+        <v>2.718</v>
       </c>
       <c r="I27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.099</v>
+        <v>0.098</v>
       </c>
       <c r="J27" s="16" t="n">
         <f aca="false">Chạy!M62</f>
@@ -17587,11 +17587,11 @@
       </c>
       <c r="K27" s="16" t="n">
         <f aca="false">J27+L27</f>
-        <v>2.91</v>
+        <v>2.898</v>
       </c>
       <c r="L27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.1</v>
+        <v>0.088</v>
       </c>
       <c r="M27" s="16" t="n">
         <f aca="false">Chạy!O62</f>
@@ -17599,11 +17599,11 @@
       </c>
       <c r="N27" s="16" t="n">
         <f aca="false">M27+O27</f>
-        <v>2.907</v>
+        <v>2.908</v>
       </c>
       <c r="O27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.097</v>
+        <v>0.098</v>
       </c>
       <c r="P27" s="17"/>
       <c r="Q27" s="18" t="n">
@@ -17627,11 +17627,11 @@
       </c>
       <c r="E28" s="16" t="n">
         <f aca="false">D28+F28</f>
-        <v>2.995</v>
+        <v>2.91</v>
       </c>
       <c r="F28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.085</v>
+        <v>0</v>
       </c>
       <c r="G28" s="16" t="n">
         <f aca="false">Chạy!I66</f>
@@ -17639,11 +17639,11 @@
       </c>
       <c r="H28" s="16" t="n">
         <f aca="false">G28+I28</f>
-        <v>2.628</v>
+        <v>2.627</v>
       </c>
       <c r="I28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="J28" s="16" t="n">
         <f aca="false">Chạy!M70</f>
@@ -17651,11 +17651,11 @@
       </c>
       <c r="K28" s="16" t="n">
         <f aca="false">J28+L28</f>
-        <v>2.859</v>
+        <v>2.9</v>
       </c>
       <c r="L28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.049</v>
+        <v>0.09</v>
       </c>
       <c r="M28" s="16" t="n">
         <f aca="false">Chạy!O70</f>
@@ -17663,11 +17663,11 @@
       </c>
       <c r="N28" s="16" t="n">
         <f aca="false">M28+O28</f>
-        <v>2.858</v>
+        <v>2.897</v>
       </c>
       <c r="O28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-30,100)/1000</f>
-        <v>0.048</v>
+        <v>0.087</v>
       </c>
       <c r="P28" s="17"/>
       <c r="Q28" s="18"/>
@@ -17826,7 +17826,7 @@
     <row r="2" s="75" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="27" t="str">
         <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,4,0)</f>
-        <v xml:space="preserve">Kèm theo BBNT số: 23.NĐXB6A/CVXD ngày 06 tháng 09 năm 2026</v>
+        <v xml:space="preserve">Kèm theo BBNT số: 23.NĐXB6A/CVXD ngày 09 tháng 09 năm 2026</v>
       </c>
       <c r="B2" s="27"/>
       <c r="C2" s="27"/>
